--- a/2019ElectionPolls.xlsx
+++ b/2019ElectionPolls.xlsx
@@ -213,68 +213,72 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -604,40 +608,43 @@
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
+      <c r="M2" s="7" t="n">
+        <f aca="false">(A2+B2)/2</f>
+        <v>42555</v>
+      </c>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="8" t="n">
         <v>42556</v>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="8" t="n">
         <v>42568</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="9" t="n">
+      <c r="D3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G3" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9" t="n">
+      <c r="G3" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="K3" s="9"/>
+      <c r="K3" s="10"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
@@ -679,35 +686,35 @@
       <c r="O4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="8" t="n">
         <v>42572</v>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>42583</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="9" t="n">
+      <c r="D5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9" t="n">
+      <c r="G5" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="9"/>
+      <c r="K5" s="10"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -749,35 +756,35 @@
       <c r="O6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="8" t="n">
         <v>42587</v>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>42597</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="9" t="n">
+      <c r="D7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9" t="n">
+      <c r="G7" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="9"/>
+      <c r="K7" s="10"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
@@ -819,33 +826,33 @@
       <c r="O8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="8" t="n">
         <v>42607</v>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <v>42610</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="9" t="n">
+      <c r="D9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>1696</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="G9" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H9" s="9" t="n">
+      <c r="G9" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H9" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
@@ -887,37 +894,37 @@
       <c r="O10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="8" t="n">
         <v>42608</v>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="8" t="n">
         <v>42618</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="9" t="n">
+      <c r="D11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G11" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I11" s="9" t="n">
+      <c r="G11" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="9"/>
+      <c r="K11" s="10"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
@@ -957,37 +964,37 @@
       <c r="O12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="8" t="n">
         <v>42615</v>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="8" t="n">
         <v>42625</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="9" t="n">
+      <c r="D13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G13" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" s="9" t="n">
+      <c r="G13" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="K13" s="9"/>
+      <c r="K13" s="10"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
@@ -1031,33 +1038,33 @@
       <c r="O14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="8" t="n">
         <v>42635</v>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <v>42638</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="9" t="n">
+      <c r="D15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="10" t="n">
         <v>1662</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="G15" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H15" s="9" t="n">
+      <c r="G15" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H15" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
@@ -1101,37 +1108,37 @@
       <c r="O16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="8" t="n">
         <v>42636</v>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="8" t="n">
         <v>42646</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="9" t="n">
+      <c r="D17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="G17" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H17" s="9" t="n">
+      <c r="G17" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H17" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J17" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K17" s="9"/>
+      <c r="K17" s="10"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
@@ -1171,37 +1178,37 @@
       <c r="O18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="8" t="n">
         <v>42643</v>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="8" t="n">
         <v>42653</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="9" t="n">
+      <c r="D19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G19" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I19" s="9" t="n">
+      <c r="G19" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K19" s="9"/>
+      <c r="K19" s="10"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
@@ -1245,33 +1252,33 @@
       <c r="O20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="8" t="n">
         <v>42663</v>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="8" t="n">
         <v>42666</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="9" t="n">
+      <c r="D21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="10" t="n">
         <v>1673</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G21" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
+      <c r="G21" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
@@ -1315,37 +1322,37 @@
       <c r="O22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="8" t="n">
         <v>42664</v>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="8" t="n">
         <v>42674</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="9" t="n">
+      <c r="D23" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G23" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I23" s="9" t="n">
+      <c r="G23" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J23" s="9" t="n">
+      <c r="J23" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="K23" s="9"/>
+      <c r="K23" s="10"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
@@ -1385,37 +1392,37 @@
       <c r="O24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="8" t="n">
         <v>42671</v>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="8" t="n">
         <v>42681</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="9" t="n">
+      <c r="D25" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G25" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I25" s="9" t="n">
+      <c r="G25" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J25" s="9" t="n">
+      <c r="J25" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K25" s="9"/>
+      <c r="K25" s="10"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
@@ -1459,33 +1466,33 @@
       <c r="O26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="8" t="n">
         <v>42691</v>
       </c>
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="8" t="n">
         <v>42694</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="9" t="n">
+      <c r="D27" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="10" t="n">
         <v>1846</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H27" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
+      <c r="H27" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
@@ -1529,33 +1536,33 @@
       <c r="O28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="8" t="n">
         <v>42698</v>
       </c>
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="8" t="n">
         <v>42700</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="9" t="n">
+      <c r="D29" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="10" t="n">
         <v>1403</v>
       </c>
-      <c r="F29" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G29" s="9" t="n">
+      <c r="F29" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G29" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="H29" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
@@ -1599,37 +1606,37 @@
       <c r="O30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="8" t="n">
         <v>42698</v>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B31" s="8" t="n">
         <v>42708</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="9" t="n">
+      <c r="D31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G31" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H31" s="9" t="n">
+      <c r="G31" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H31" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I31" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K31" s="9"/>
+      <c r="K31" s="10"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
@@ -1669,37 +1676,37 @@
       <c r="O32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="8" t="n">
         <v>42705</v>
       </c>
-      <c r="B33" s="7" t="n">
+      <c r="B33" s="8" t="n">
         <v>42715</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33" s="9" t="n">
+      <c r="D33" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F33" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H33" s="9" t="n">
+      <c r="F33" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H33" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="I33" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J33" s="9" t="n">
+      <c r="J33" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K33" s="9"/>
+      <c r="K33" s="10"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
@@ -1743,37 +1750,37 @@
       <c r="O34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="8" t="n">
         <v>42755</v>
       </c>
-      <c r="B35" s="7" t="n">
+      <c r="B35" s="8" t="n">
         <v>42758</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="9" t="n">
+      <c r="D35" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="G35" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I35" s="9" t="n">
+      <c r="G35" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I35" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J35" s="9" t="n">
+      <c r="J35" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K35" s="9"/>
+      <c r="K35" s="10"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
@@ -1817,37 +1824,37 @@
       <c r="O36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="8" t="n">
         <v>42761</v>
       </c>
-      <c r="B37" s="7" t="n">
+      <c r="B37" s="8" t="n">
         <v>42771</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="9" t="n">
+      <c r="D37" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F37" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H37" s="9" t="n">
+      <c r="F37" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H37" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="I37" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J37" s="9" t="n">
+      <c r="I37" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="9"/>
+      <c r="K37" s="10"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
@@ -1887,37 +1894,37 @@
       <c r="O38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="8" t="n">
         <v>42768</v>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="B39" s="8" t="n">
         <v>42778</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" s="9" t="n">
+      <c r="D39" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F39" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G39" s="9" t="n">
+      <c r="F39" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G39" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="H39" s="9" t="n">
+      <c r="H39" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I39" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J39" s="9" t="n">
+      <c r="I39" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J39" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K39" s="9"/>
+      <c r="K39" s="10"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
@@ -1961,35 +1968,35 @@
       <c r="O40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="8" t="n">
         <v>42789</v>
       </c>
-      <c r="B41" s="7" t="n">
+      <c r="B41" s="8" t="n">
         <v>42792</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="9" t="n">
+      <c r="D41" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="10" t="n">
         <v>1582</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="G41" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H41" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
+      <c r="G41" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I41" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
@@ -2033,37 +2040,37 @@
       <c r="O42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="8" t="n">
         <v>42787</v>
       </c>
-      <c r="B43" s="7" t="n">
+      <c r="B43" s="8" t="n">
         <v>42800</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" s="9" t="n">
+      <c r="D43" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F43" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G43" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H43" s="9" t="n">
+      <c r="F43" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H43" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I43" s="9" t="n">
+      <c r="I43" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J43" s="9" t="n">
+      <c r="J43" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K43" s="9"/>
+      <c r="K43" s="10"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
@@ -2107,37 +2114,37 @@
       <c r="O44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="8" t="n">
         <v>42802</v>
       </c>
-      <c r="B45" s="7" t="n">
+      <c r="B45" s="8" t="n">
         <v>42813</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" s="9" t="n">
+      <c r="D45" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="G45" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H45" s="9" t="n">
+      <c r="G45" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H45" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I45" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J45" s="9" t="n">
+      <c r="I45" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K45" s="9"/>
+      <c r="K45" s="10"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
@@ -2179,33 +2186,33 @@
       <c r="O46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="8" t="n">
         <v>42816</v>
       </c>
-      <c r="B47" s="7" t="n">
+      <c r="B47" s="8" t="n">
         <v>42819</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" s="9" t="n">
+      <c r="D47" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="10" t="n">
         <v>1400</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="G47" s="9" t="n">
+      <c r="G47" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="H47" s="9" t="n">
+      <c r="H47" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
@@ -2249,37 +2256,37 @@
       <c r="O48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="8" t="n">
         <v>42816</v>
       </c>
-      <c r="B49" s="7" t="n">
+      <c r="B49" s="8" t="n">
         <v>42827</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="9" t="n">
+      <c r="D49" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F49" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G49" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H49" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I49" s="9" t="n">
+      <c r="F49" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I49" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J49" s="9" t="n">
+      <c r="J49" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K49" s="9"/>
+      <c r="K49" s="10"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
@@ -2321,37 +2328,37 @@
       <c r="O50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="8" t="n">
         <v>42823</v>
       </c>
-      <c r="B51" s="7" t="n">
+      <c r="B51" s="8" t="n">
         <v>42834</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="9" t="n">
+      <c r="D51" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F51" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G51" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H51" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I51" s="9" t="n">
+      <c r="F51" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J51" s="9" t="n">
+      <c r="J51" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K51" s="9"/>
+      <c r="K51" s="10"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
@@ -2395,37 +2402,37 @@
       <c r="O52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="8" t="n">
         <v>42837</v>
       </c>
-      <c r="B53" s="7" t="n">
+      <c r="B53" s="8" t="n">
         <v>42848</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D53" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="9" t="n">
+      <c r="D53" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F53" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G53" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H53" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I53" s="9" t="n">
+      <c r="F53" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J53" s="9" t="n">
+      <c r="J53" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K53" s="9"/>
+      <c r="K53" s="10"/>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
@@ -2467,37 +2474,37 @@
       <c r="O54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="8" t="n">
         <v>42845</v>
       </c>
-      <c r="B55" s="7" t="n">
+      <c r="B55" s="8" t="n">
         <v>42856</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="9" t="n">
+      <c r="D55" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F55" s="9" t="n">
+      <c r="F55" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G55" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H55" s="9" t="n">
+      <c r="G55" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H55" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I55" s="9" t="n">
+      <c r="I55" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J55" s="9" t="n">
+      <c r="J55" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K55" s="9"/>
+      <c r="K55" s="10"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
@@ -2541,33 +2548,33 @@
       <c r="O56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="8" t="n">
         <v>42865</v>
       </c>
-      <c r="B57" s="7" t="n">
+      <c r="B57" s="8" t="n">
         <v>42868</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D57" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E57" s="9" t="n">
+      <c r="D57" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" s="10" t="n">
         <v>1401</v>
       </c>
-      <c r="F57" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G57" s="9" t="n">
+      <c r="F57" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G57" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="H57" s="9" t="n">
+      <c r="H57" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="I57" s="9"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
@@ -2609,37 +2616,37 @@
       <c r="O58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="8" t="n">
         <v>42859</v>
       </c>
-      <c r="B59" s="7" t="n">
+      <c r="B59" s="8" t="n">
         <v>42870</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D59" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" s="9" t="n">
+      <c r="D59" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F59" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G59" s="9" t="n">
+      <c r="F59" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G59" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H59" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I59" s="9" t="n">
+      <c r="H59" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I59" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J59" s="9" t="n">
+      <c r="J59" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K59" s="9"/>
+      <c r="K59" s="10"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
@@ -2683,35 +2690,35 @@
       <c r="O60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="n">
+      <c r="A61" s="8" t="n">
         <v>42880</v>
       </c>
-      <c r="B61" s="7" t="n">
+      <c r="B61" s="8" t="n">
         <v>42883</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="9" t="n">
+      <c r="D61" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="10" t="n">
         <v>1716</v>
       </c>
-      <c r="F61" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G61" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H61" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I61" s="9" t="n">
+      <c r="F61" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H61" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I61" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
@@ -2755,37 +2762,37 @@
       <c r="O62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="7" t="n">
+      <c r="A63" s="8" t="n">
         <v>42880</v>
       </c>
-      <c r="B63" s="7" t="n">
+      <c r="B63" s="8" t="n">
         <v>42892</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D63" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="9" t="n">
+      <c r="D63" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F63" s="9" t="n">
+      <c r="F63" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G63" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H63" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I63" s="9" t="n">
+      <c r="G63" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H63" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I63" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J63" s="9" t="n">
+      <c r="J63" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K63" s="9"/>
+      <c r="K63" s="10"/>
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
@@ -2829,35 +2836,35 @@
       <c r="O64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="n">
+      <c r="A65" s="8" t="n">
         <v>42901</v>
       </c>
-      <c r="B65" s="7" t="n">
+      <c r="B65" s="8" t="n">
         <v>42904</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D65" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" s="9" t="n">
+      <c r="D65" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="10" t="n">
         <v>1786</v>
       </c>
-      <c r="F65" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G65" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H65" s="9" t="n">
+      <c r="F65" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H65" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I65" s="9" t="n">
+      <c r="I65" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="J65" s="9"/>
-      <c r="K65" s="9"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
@@ -2901,35 +2908,35 @@
       <c r="O66" s="6"/>
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7" t="n">
+      <c r="A67" s="8" t="n">
         <v>42908</v>
       </c>
-      <c r="B67" s="7" t="n">
+      <c r="B67" s="8" t="n">
         <v>42911</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D67" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="9" t="n">
+      <c r="D67" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="F67" s="9" t="n">
+      <c r="F67" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="G67" s="9" t="n">
+      <c r="G67" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="H67" s="9" t="n">
+      <c r="H67" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="I67" s="9" t="n">
+      <c r="I67" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J67" s="9"/>
-      <c r="K67" s="9"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
@@ -2973,35 +2980,35 @@
       <c r="O68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7" t="n">
+      <c r="A69" s="8" t="n">
         <v>42915</v>
       </c>
-      <c r="B69" s="7" t="n">
+      <c r="B69" s="8" t="n">
         <v>42915</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D69" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="9" t="n">
+      <c r="D69" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="10" t="n">
         <v>2389</v>
       </c>
-      <c r="F69" s="9" t="n">
+      <c r="F69" s="10" t="n">
         <v>36.4</v>
       </c>
-      <c r="G69" s="9" t="n">
+      <c r="G69" s="10" t="n">
         <v>35.4</v>
       </c>
-      <c r="H69" s="9" t="n">
+      <c r="H69" s="10" t="n">
         <v>10.2</v>
       </c>
-      <c r="I69" s="9" t="n">
+      <c r="I69" s="10" t="n">
         <v>9.6</v>
       </c>
-      <c r="J69" s="9"/>
-      <c r="K69" s="9"/>
+      <c r="J69" s="10"/>
+      <c r="K69" s="10"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
@@ -3045,35 +3052,35 @@
       <c r="O70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="n">
+      <c r="A71" s="8" t="n">
         <v>42922</v>
       </c>
-      <c r="B71" s="7" t="n">
+      <c r="B71" s="8" t="n">
         <v>42925</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D71" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" s="9" t="n">
+      <c r="D71" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="10" t="n">
         <v>1597</v>
       </c>
-      <c r="F71" s="9" t="n">
+      <c r="F71" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="G71" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H71" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I71" s="9" t="n">
+      <c r="G71" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H71" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I71" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="J71" s="9"/>
-      <c r="K71" s="9"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
@@ -3115,37 +3122,37 @@
       <c r="O72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="n">
+      <c r="A73" s="8" t="n">
         <v>42916</v>
       </c>
-      <c r="B73" s="7" t="n">
+      <c r="B73" s="8" t="n">
         <v>42926</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D73" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73" s="9" t="n">
+      <c r="D73" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F73" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G73" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H73" s="9" t="n">
+      <c r="F73" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G73" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H73" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I73" s="9" t="n">
+      <c r="I73" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J73" s="9" t="n">
+      <c r="J73" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K73" s="9"/>
+      <c r="K73" s="10"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
@@ -3189,35 +3196,35 @@
       <c r="O74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="7" t="n">
+      <c r="A75" s="8" t="n">
         <v>42935</v>
       </c>
-      <c r="B75" s="7" t="n">
+      <c r="B75" s="8" t="n">
         <v>42935</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D75" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E75" s="9" t="n">
+      <c r="D75" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="10" t="n">
         <v>2300</v>
       </c>
-      <c r="F75" s="9" t="n">
+      <c r="F75" s="10" t="n">
         <v>37.2</v>
       </c>
-      <c r="G75" s="9" t="n">
+      <c r="G75" s="10" t="n">
         <v>35.1</v>
       </c>
-      <c r="H75" s="9" t="n">
+      <c r="H75" s="10" t="n">
         <v>8.8</v>
       </c>
-      <c r="I75" s="9" t="n">
+      <c r="I75" s="10" t="n">
         <v>11.7</v>
       </c>
-      <c r="J75" s="9"/>
-      <c r="K75" s="9"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="10"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
@@ -3259,35 +3266,35 @@
       <c r="O76" s="6"/>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="n">
+      <c r="A77" s="8" t="n">
         <v>42936</v>
       </c>
-      <c r="B77" s="7" t="n">
+      <c r="B77" s="8" t="n">
         <v>42939</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D77" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E77" s="9" t="n">
+      <c r="D77" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="10" t="n">
         <v>1005</v>
       </c>
-      <c r="F77" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G77" s="9" t="n">
+      <c r="F77" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G77" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="H77" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I77" s="9" t="n">
+      <c r="H77" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I77" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J77" s="9"/>
-      <c r="K77" s="9"/>
+      <c r="J77" s="10"/>
+      <c r="K77" s="10"/>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
@@ -3331,37 +3338,37 @@
       <c r="O78" s="6"/>
     </row>
     <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="7" t="n">
+      <c r="A79" s="8" t="n">
         <v>42937</v>
       </c>
-      <c r="B79" s="7" t="n">
+      <c r="B79" s="8" t="n">
         <v>42947</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D79" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79" s="9" t="n">
+      <c r="D79" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F79" s="9" t="n">
+      <c r="F79" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G79" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H79" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I79" s="9" t="n">
+      <c r="G79" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H79" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I79" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J79" s="9" t="n">
+      <c r="J79" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="K79" s="9"/>
+      <c r="K79" s="10"/>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
       <c r="N79" s="6"/>
@@ -3403,37 +3410,37 @@
       <c r="O80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7" t="n">
+      <c r="A81" s="8" t="n">
         <v>42950</v>
       </c>
-      <c r="B81" s="7" t="n">
+      <c r="B81" s="8" t="n">
         <v>42953</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D81" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E81" s="9" t="n">
+      <c r="D81" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="10" t="n">
         <v>1076</v>
       </c>
-      <c r="F81" s="9" t="n">
+      <c r="F81" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="G81" s="9" t="n">
+      <c r="G81" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="H81" s="9" t="n">
+      <c r="H81" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I81" s="9" t="n">
+      <c r="I81" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J81" s="9" t="n">
+      <c r="J81" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="K81" s="9"/>
+      <c r="K81" s="10"/>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
       <c r="N81" s="6"/>
@@ -3477,37 +3484,37 @@
       <c r="O82" s="6"/>
     </row>
     <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="7" t="n">
+      <c r="A83" s="8" t="n">
         <v>42951</v>
       </c>
-      <c r="B83" s="7" t="n">
+      <c r="B83" s="8" t="n">
         <v>42961</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D83" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E83" s="9" t="n">
+      <c r="D83" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F83" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G83" s="9" t="n">
+      <c r="F83" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G83" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="H83" s="9" t="n">
+      <c r="H83" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I83" s="9" t="n">
+      <c r="I83" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J83" s="9" t="n">
+      <c r="J83" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="K83" s="9"/>
+      <c r="K83" s="10"/>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
       <c r="N83" s="6"/>
@@ -3549,37 +3556,37 @@
       <c r="O84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7" t="n">
+      <c r="A85" s="8" t="n">
         <v>42964</v>
       </c>
-      <c r="B85" s="7" t="n">
+      <c r="B85" s="8" t="n">
         <v>42967</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D85" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E85" s="9" t="n">
+      <c r="D85" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="10" t="n">
         <v>1012</v>
       </c>
-      <c r="F85" s="9" t="n">
+      <c r="F85" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="G85" s="9" t="n">
+      <c r="G85" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="H85" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I85" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J85" s="9" t="n">
+      <c r="H85" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I85" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J85" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="K85" s="9"/>
+      <c r="K85" s="10"/>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
       <c r="N85" s="6"/>
@@ -3623,35 +3630,35 @@
       <c r="O86" s="6"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="7" t="n">
+      <c r="A87" s="8" t="n">
         <v>42970</v>
       </c>
-      <c r="B87" s="7" t="n">
+      <c r="B87" s="8" t="n">
         <v>42970</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D87" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" s="9" t="n">
+      <c r="D87" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="10" t="n">
         <v>2832</v>
       </c>
-      <c r="F87" s="9" t="n">
+      <c r="F87" s="10" t="n">
         <v>34.5</v>
       </c>
-      <c r="G87" s="9" t="n">
+      <c r="G87" s="10" t="n">
         <v>36.7</v>
       </c>
-      <c r="H87" s="9" t="n">
+      <c r="H87" s="10" t="n">
         <v>10.3</v>
       </c>
-      <c r="I87" s="9" t="n">
+      <c r="I87" s="10" t="n">
         <v>10.4</v>
       </c>
-      <c r="J87" s="9"/>
-      <c r="K87" s="9"/>
+      <c r="J87" s="10"/>
+      <c r="K87" s="10"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
       <c r="N87" s="6"/>
@@ -3695,35 +3702,35 @@
       <c r="O88" s="6"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7" t="n">
+      <c r="A89" s="8" t="n">
         <v>42978</v>
       </c>
-      <c r="B89" s="7" t="n">
+      <c r="B89" s="8" t="n">
         <v>42981</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D89" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E89" s="9" t="n">
+      <c r="D89" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" s="10" t="n">
         <v>1606</v>
       </c>
-      <c r="F89" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G89" s="9" t="n">
+      <c r="F89" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G89" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H89" s="9" t="n">
+      <c r="H89" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I89" s="9" t="n">
+      <c r="I89" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J89" s="9"/>
-      <c r="K89" s="9"/>
+      <c r="J89" s="10"/>
+      <c r="K89" s="10"/>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
@@ -3765,37 +3772,37 @@
       <c r="O90" s="6"/>
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="7" t="n">
+      <c r="A91" s="8" t="n">
         <v>42972</v>
       </c>
-      <c r="B91" s="7" t="n">
+      <c r="B91" s="8" t="n">
         <v>42982</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D91" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E91" s="9" t="n">
+      <c r="D91" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E91" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F91" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G91" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H91" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I91" s="9" t="n">
+      <c r="F91" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G91" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H91" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I91" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J91" s="9" t="n">
+      <c r="J91" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="K91" s="9"/>
+      <c r="K91" s="10"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
@@ -3835,37 +3842,37 @@
       <c r="O92" s="6"/>
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="7" t="n">
+      <c r="A93" s="8" t="n">
         <v>42979</v>
       </c>
-      <c r="B93" s="7" t="n">
+      <c r="B93" s="8" t="n">
         <v>42988</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D93" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E93" s="9" t="n">
+      <c r="D93" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F93" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G93" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H93" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I93" s="9" t="n">
+      <c r="F93" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G93" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H93" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I93" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J93" s="9" t="n">
+      <c r="J93" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="K93" s="9"/>
+      <c r="K93" s="10"/>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
       <c r="N93" s="6"/>
@@ -3909,37 +3916,37 @@
       <c r="O94" s="6"/>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="7" t="n">
+      <c r="A95" s="8" t="n">
         <v>42992</v>
       </c>
-      <c r="B95" s="7" t="n">
+      <c r="B95" s="8" t="n">
         <v>42995</v>
       </c>
-      <c r="C95" s="8" t="s">
+      <c r="C95" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D95" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E95" s="9" t="n">
+      <c r="D95" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E95" s="10" t="n">
         <v>1056</v>
       </c>
-      <c r="F95" s="9" t="n">
+      <c r="F95" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="G95" s="9" t="n">
+      <c r="G95" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="H95" s="9" t="n">
+      <c r="H95" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I95" s="9" t="n">
+      <c r="I95" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J95" s="9" t="n">
+      <c r="J95" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K95" s="9"/>
+      <c r="K95" s="10"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
       <c r="N95" s="6"/>
@@ -3983,35 +3990,35 @@
       <c r="O96" s="6"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="7" t="n">
+      <c r="A97" s="8" t="n">
         <v>42999</v>
       </c>
-      <c r="B97" s="7" t="n">
+      <c r="B97" s="8" t="n">
         <v>43002</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D97" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" s="9" t="n">
+      <c r="D97" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="10" t="n">
         <v>1695</v>
       </c>
-      <c r="F97" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G97" s="9" t="n">
+      <c r="F97" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G97" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H97" s="9" t="n">
+      <c r="H97" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I97" s="9" t="n">
+      <c r="I97" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J97" s="9"/>
-      <c r="K97" s="9"/>
+      <c r="J97" s="10"/>
+      <c r="K97" s="10"/>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
       <c r="N97" s="6"/>
@@ -4053,37 +4060,37 @@
       <c r="O98" s="6"/>
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="7" t="n">
+      <c r="A99" s="8" t="n">
         <v>42999</v>
       </c>
-      <c r="B99" s="7" t="n">
+      <c r="B99" s="8" t="n">
         <v>43009</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C99" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D99" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" s="9" t="n">
+      <c r="D99" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F99" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G99" s="9" t="n">
+      <c r="F99" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G99" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H99" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I99" s="9" t="n">
+      <c r="H99" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I99" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J99" s="9" t="n">
+      <c r="J99" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K99" s="9"/>
+      <c r="K99" s="10"/>
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
       <c r="N99" s="6"/>
@@ -4127,37 +4134,37 @@
       <c r="O100" s="6"/>
     </row>
     <row r="101" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="7" t="n">
+      <c r="A101" s="8" t="n">
         <v>43006</v>
       </c>
-      <c r="B101" s="7" t="n">
+      <c r="B101" s="8" t="n">
         <v>43016</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C101" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D101" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E101" s="9" t="n">
+      <c r="D101" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E101" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F101" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G101" s="9" t="n">
+      <c r="F101" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G101" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H101" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I101" s="9" t="n">
+      <c r="H101" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I101" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J101" s="9" t="n">
+      <c r="J101" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="K101" s="9"/>
+      <c r="K101" s="10"/>
       <c r="L101" s="6"/>
       <c r="M101" s="6"/>
       <c r="N101" s="6"/>
@@ -4201,35 +4208,35 @@
       <c r="O102" s="6"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7" t="n">
+      <c r="A103" s="8" t="n">
         <v>43020</v>
       </c>
-      <c r="B103" s="7" t="n">
+      <c r="B103" s="8" t="n">
         <v>43023</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D103" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E103" s="9" t="n">
+      <c r="D103" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" s="10" t="n">
         <v>1583</v>
       </c>
-      <c r="F103" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G103" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H103" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I103" s="9" t="n">
+      <c r="F103" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G103" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H103" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I103" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J103" s="9"/>
-      <c r="K103" s="9"/>
+      <c r="J103" s="10"/>
+      <c r="K103" s="10"/>
       <c r="L103" s="6"/>
       <c r="M103" s="6"/>
       <c r="N103" s="6"/>
@@ -4273,37 +4280,37 @@
       <c r="O104" s="6"/>
     </row>
     <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="7" t="n">
+      <c r="A105" s="8" t="n">
         <v>43021</v>
       </c>
-      <c r="B105" s="7" t="n">
+      <c r="B105" s="8" t="n">
         <v>43031</v>
       </c>
-      <c r="C105" s="8" t="s">
+      <c r="C105" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D105" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E105" s="9" t="n">
+      <c r="D105" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F105" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G105" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H105" s="9" t="n">
+      <c r="F105" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G105" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H105" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I105" s="9" t="n">
+      <c r="I105" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J105" s="9" t="n">
+      <c r="J105" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K105" s="9"/>
+      <c r="K105" s="10"/>
       <c r="L105" s="6"/>
       <c r="M105" s="6"/>
       <c r="N105" s="6"/>
@@ -4345,35 +4352,35 @@
       <c r="O106" s="6"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="7" t="n">
+      <c r="A107" s="8" t="n">
         <v>43034</v>
       </c>
-      <c r="B107" s="7" t="n">
+      <c r="B107" s="8" t="n">
         <v>43037</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D107" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E107" s="9" t="n">
+      <c r="D107" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E107" s="10" t="n">
         <v>1623</v>
       </c>
-      <c r="F107" s="9" t="n">
+      <c r="F107" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="G107" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H107" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I107" s="9" t="n">
+      <c r="G107" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H107" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I107" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J107" s="9"/>
-      <c r="K107" s="9"/>
+      <c r="J107" s="10"/>
+      <c r="K107" s="10"/>
       <c r="L107" s="6"/>
       <c r="M107" s="6"/>
       <c r="N107" s="6"/>
@@ -4417,37 +4424,37 @@
       <c r="O108" s="6"/>
     </row>
     <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7" t="n">
+      <c r="A109" s="8" t="n">
         <v>43028</v>
       </c>
-      <c r="B109" s="7" t="n">
+      <c r="B109" s="8" t="n">
         <v>43038</v>
       </c>
-      <c r="C109" s="8" t="s">
+      <c r="C109" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D109" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E109" s="9" t="n">
+      <c r="D109" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F109" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G109" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H109" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I109" s="9" t="n">
+      <c r="F109" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G109" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H109" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I109" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J109" s="9" t="n">
+      <c r="J109" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K109" s="9"/>
+      <c r="K109" s="10"/>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
       <c r="N109" s="6"/>
@@ -4491,35 +4498,35 @@
       <c r="O110" s="6"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="7" t="n">
+      <c r="A111" s="8" t="n">
         <v>43048</v>
       </c>
-      <c r="B111" s="7" t="n">
+      <c r="B111" s="8" t="n">
         <v>43051</v>
       </c>
-      <c r="C111" s="8" t="s">
+      <c r="C111" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D111" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E111" s="9" t="n">
+      <c r="D111" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E111" s="10" t="n">
         <v>1624</v>
       </c>
-      <c r="F111" s="9" t="n">
+      <c r="F111" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="G111" s="9" t="n">
+      <c r="G111" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H111" s="9" t="n">
+      <c r="H111" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I111" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J111" s="9"/>
-      <c r="K111" s="9"/>
+      <c r="I111" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J111" s="10"/>
+      <c r="K111" s="10"/>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
       <c r="N111" s="6"/>
@@ -4563,37 +4570,37 @@
       <c r="O112" s="6"/>
     </row>
     <row r="113" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="7" t="n">
+      <c r="A113" s="8" t="n">
         <v>43042</v>
       </c>
-      <c r="B113" s="7" t="n">
+      <c r="B113" s="8" t="n">
         <v>43052</v>
       </c>
-      <c r="C113" s="8" t="s">
+      <c r="C113" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D113" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E113" s="9" t="n">
+      <c r="D113" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E113" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F113" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G113" s="9" t="n">
+      <c r="F113" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G113" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H113" s="9" t="n">
+      <c r="H113" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I113" s="9" t="n">
+      <c r="I113" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J113" s="9" t="n">
+      <c r="J113" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="K113" s="9"/>
+      <c r="K113" s="10"/>
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
       <c r="N113" s="6"/>
@@ -4637,35 +4644,35 @@
       <c r="O114" s="6"/>
     </row>
     <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="7" t="n">
+      <c r="A115" s="8" t="n">
         <v>43062</v>
       </c>
-      <c r="B115" s="7" t="n">
+      <c r="B115" s="8" t="n">
         <v>43065</v>
       </c>
-      <c r="C115" s="8" t="s">
+      <c r="C115" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D115" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E115" s="9" t="n">
+      <c r="D115" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E115" s="10" t="n">
         <v>1034</v>
       </c>
-      <c r="F115" s="9" t="n">
+      <c r="F115" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="G115" s="9" t="n">
+      <c r="G115" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="H115" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I115" s="9" t="n">
+      <c r="H115" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I115" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="J115" s="9"/>
-      <c r="K115" s="9"/>
+      <c r="J115" s="10"/>
+      <c r="K115" s="10"/>
       <c r="L115" s="6"/>
       <c r="M115" s="6"/>
       <c r="N115" s="6"/>
@@ -4709,35 +4716,35 @@
       <c r="O116" s="6"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="7" t="n">
+      <c r="A117" s="8" t="n">
         <v>43067</v>
       </c>
-      <c r="B117" s="7" t="n">
+      <c r="B117" s="8" t="n">
         <v>43067</v>
       </c>
-      <c r="C117" s="8" t="s">
+      <c r="C117" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D117" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E117" s="9" t="n">
+      <c r="D117" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E117" s="10" t="n">
         <v>4571</v>
       </c>
-      <c r="F117" s="9" t="n">
+      <c r="F117" s="10" t="n">
         <v>35.4</v>
       </c>
-      <c r="G117" s="9" t="n">
+      <c r="G117" s="10" t="n">
         <v>38.4</v>
       </c>
-      <c r="H117" s="9" t="n">
+      <c r="H117" s="10" t="n">
         <v>10.4</v>
       </c>
-      <c r="I117" s="9" t="n">
+      <c r="I117" s="10" t="n">
         <v>8.9</v>
       </c>
-      <c r="J117" s="9"/>
-      <c r="K117" s="9"/>
+      <c r="J117" s="10"/>
+      <c r="K117" s="10"/>
       <c r="L117" s="6"/>
       <c r="M117" s="6"/>
       <c r="N117" s="6"/>
@@ -4777,35 +4784,35 @@
       <c r="O118" s="6"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="7" t="n">
+      <c r="A119" s="8" t="n">
         <v>43069</v>
       </c>
-      <c r="B119" s="7" t="n">
+      <c r="B119" s="8" t="n">
         <v>43072</v>
       </c>
-      <c r="C119" s="8" t="s">
+      <c r="C119" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D119" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E119" s="9" t="n">
+      <c r="D119" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" s="10" t="n">
         <v>1560</v>
       </c>
-      <c r="F119" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G119" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H119" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I119" s="9" t="n">
+      <c r="F119" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G119" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H119" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I119" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J119" s="9"/>
-      <c r="K119" s="9"/>
+      <c r="J119" s="10"/>
+      <c r="K119" s="10"/>
       <c r="L119" s="6"/>
       <c r="M119" s="6"/>
       <c r="N119" s="6"/>
@@ -4849,37 +4856,37 @@
       <c r="O120" s="6"/>
     </row>
     <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="7" t="n">
+      <c r="A121" s="8" t="n">
         <v>43070</v>
       </c>
-      <c r="B121" s="7" t="n">
+      <c r="B121" s="8" t="n">
         <v>43080</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D121" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E121" s="9" t="n">
+      <c r="D121" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F121" s="9" t="n">
+      <c r="F121" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="G121" s="9" t="n">
+      <c r="G121" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H121" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I121" s="9" t="n">
+      <c r="H121" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I121" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J121" s="9" t="n">
+      <c r="J121" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="K121" s="9"/>
+      <c r="K121" s="10"/>
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
       <c r="N121" s="6"/>
@@ -4921,37 +4928,37 @@
       <c r="O122" s="6"/>
     </row>
     <row r="123" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="7" t="n">
+      <c r="A123" s="8" t="n">
         <v>43077</v>
       </c>
-      <c r="B123" s="7" t="n">
+      <c r="B123" s="8" t="n">
         <v>43087</v>
       </c>
-      <c r="C123" s="8" t="s">
+      <c r="C123" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D123" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E123" s="9" t="n">
+      <c r="D123" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E123" s="10" t="n">
         <v>2000</v>
       </c>
-      <c r="F123" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G123" s="9" t="n">
+      <c r="F123" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G123" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H123" s="9" t="n">
+      <c r="H123" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I123" s="9" t="n">
+      <c r="I123" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J123" s="9" t="n">
+      <c r="J123" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="K123" s="9"/>
+      <c r="K123" s="10"/>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
       <c r="N123" s="6"/>
@@ -4995,35 +5002,35 @@
       <c r="O124" s="6"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="7" t="n">
+      <c r="A125" s="8" t="n">
         <v>43125</v>
       </c>
-      <c r="B125" s="7" t="n">
+      <c r="B125" s="8" t="n">
         <v>43125</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D125" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E125" s="9" t="n">
+      <c r="D125" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E125" s="10" t="n">
         <v>2400</v>
       </c>
-      <c r="F125" s="9" t="n">
+      <c r="F125" s="10" t="n">
         <v>36.6</v>
       </c>
-      <c r="G125" s="9" t="n">
+      <c r="G125" s="10" t="n">
         <v>38.7</v>
       </c>
-      <c r="H125" s="9" t="n">
+      <c r="H125" s="10" t="n">
         <v>10.8</v>
       </c>
-      <c r="I125" s="9" t="n">
+      <c r="I125" s="10" t="n">
         <v>8.6</v>
       </c>
-      <c r="J125" s="9"/>
-      <c r="K125" s="9"/>
+      <c r="J125" s="10"/>
+      <c r="K125" s="10"/>
       <c r="L125" s="6"/>
       <c r="M125" s="6"/>
       <c r="N125" s="6"/>
@@ -5067,35 +5074,35 @@
       <c r="O126" s="6"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="7" t="n">
+      <c r="A127" s="8" t="n">
         <v>43132</v>
       </c>
-      <c r="B127" s="7" t="n">
+      <c r="B127" s="8" t="n">
         <v>43135</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D127" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E127" s="9" t="n">
+      <c r="D127" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E127" s="10" t="n">
         <v>1616</v>
       </c>
-      <c r="F127" s="9" t="n">
+      <c r="F127" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G127" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H127" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I127" s="9" t="n">
+      <c r="G127" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H127" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I127" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J127" s="9"/>
-      <c r="K127" s="9"/>
+      <c r="J127" s="10"/>
+      <c r="K127" s="10"/>
       <c r="L127" s="6"/>
       <c r="M127" s="6"/>
       <c r="N127" s="6"/>
@@ -5139,35 +5146,35 @@
       <c r="O128" s="6"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="7" t="n">
+      <c r="A129" s="8" t="n">
         <v>43146</v>
       </c>
-      <c r="B129" s="7" t="n">
+      <c r="B129" s="8" t="n">
         <v>43149</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D129" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E129" s="9" t="n">
+      <c r="D129" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E129" s="10" t="n">
         <v>1609</v>
       </c>
-      <c r="F129" s="9" t="n">
+      <c r="F129" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G129" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H129" s="9" t="n">
+      <c r="G129" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H129" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I129" s="9" t="n">
+      <c r="I129" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J129" s="9"/>
-      <c r="K129" s="9"/>
+      <c r="J129" s="10"/>
+      <c r="K129" s="10"/>
       <c r="L129" s="6"/>
       <c r="M129" s="6"/>
       <c r="N129" s="6"/>
@@ -5209,35 +5216,35 @@
       <c r="O130" s="6"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="7" t="n">
+      <c r="A131" s="8" t="n">
         <v>43153</v>
       </c>
-      <c r="B131" s="7" t="n">
+      <c r="B131" s="8" t="n">
         <v>43153</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D131" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E131" s="9" t="n">
+      <c r="D131" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E131" s="10" t="n">
         <v>2400</v>
       </c>
-      <c r="F131" s="9" t="n">
+      <c r="F131" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="G131" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H131" s="9" t="n">
+      <c r="G131" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H131" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I131" s="9" t="n">
+      <c r="I131" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J131" s="9"/>
-      <c r="K131" s="9"/>
+      <c r="J131" s="10"/>
+      <c r="K131" s="10"/>
       <c r="L131" s="6"/>
       <c r="M131" s="6"/>
       <c r="N131" s="6"/>
@@ -5281,35 +5288,35 @@
       <c r="O132" s="6"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="7" t="n">
+      <c r="A133" s="8" t="n">
         <v>43160</v>
       </c>
-      <c r="B133" s="7" t="n">
+      <c r="B133" s="8" t="n">
         <v>43163</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D133" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E133" s="9" t="n">
+      <c r="D133" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E133" s="10" t="n">
         <v>1657</v>
       </c>
-      <c r="F133" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G133" s="9" t="n">
+      <c r="F133" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G133" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H133" s="9" t="n">
+      <c r="H133" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I133" s="9" t="n">
+      <c r="I133" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J133" s="9"/>
-      <c r="K133" s="9"/>
+      <c r="J133" s="10"/>
+      <c r="K133" s="10"/>
       <c r="L133" s="6"/>
       <c r="M133" s="6"/>
       <c r="N133" s="6"/>
@@ -5353,35 +5360,35 @@
       <c r="O134" s="6"/>
     </row>
     <row r="135" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="7" t="n">
+      <c r="A135" s="8" t="n">
         <v>43165</v>
       </c>
-      <c r="B135" s="7" t="n">
+      <c r="B135" s="8" t="n">
         <v>43170</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D135" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E135" s="9" t="n">
+      <c r="D135" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E135" s="10" t="n">
         <v>1089</v>
       </c>
-      <c r="F135" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G135" s="9" t="n">
+      <c r="F135" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G135" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H135" s="9" t="n">
+      <c r="H135" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="I135" s="9" t="n">
+      <c r="I135" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J135" s="9"/>
-      <c r="K135" s="9"/>
+      <c r="J135" s="10"/>
+      <c r="K135" s="10"/>
       <c r="L135" s="6"/>
       <c r="M135" s="6"/>
       <c r="N135" s="6"/>
@@ -5425,35 +5432,35 @@
       <c r="O136" s="6"/>
     </row>
     <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="7" t="n">
+      <c r="A137" s="8" t="n">
         <v>43180</v>
       </c>
-      <c r="B137" s="7" t="n">
+      <c r="B137" s="8" t="n">
         <v>43184</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D137" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E137" s="9" t="n">
+      <c r="D137" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E137" s="10" t="n">
         <v>1085</v>
       </c>
-      <c r="F137" s="9" t="n">
+      <c r="F137" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G137" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H137" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I137" s="9" t="n">
+      <c r="G137" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H137" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I137" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J137" s="9"/>
-      <c r="K137" s="9"/>
+      <c r="J137" s="10"/>
+      <c r="K137" s="10"/>
       <c r="L137" s="6"/>
       <c r="M137" s="6"/>
       <c r="N137" s="6"/>
@@ -5495,35 +5502,35 @@
       <c r="O138" s="6"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="7" t="n">
+      <c r="A139" s="8" t="n">
         <v>43187</v>
       </c>
-      <c r="B139" s="7" t="n">
+      <c r="B139" s="8" t="n">
         <v>43187</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D139" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E139" s="9" t="n">
+      <c r="D139" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E139" s="10" t="n">
         <v>2400</v>
       </c>
-      <c r="F139" s="9" t="n">
+      <c r="F139" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="G139" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H139" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I139" s="9" t="n">
+      <c r="G139" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H139" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I139" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J139" s="9"/>
-      <c r="K139" s="9"/>
+      <c r="J139" s="10"/>
+      <c r="K139" s="10"/>
       <c r="L139" s="6"/>
       <c r="M139" s="6"/>
       <c r="N139" s="6"/>
@@ -5565,35 +5572,35 @@
       <c r="O140" s="6"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="7" t="n">
+      <c r="A141" s="8" t="n">
         <v>43195</v>
       </c>
-      <c r="B141" s="7" t="n">
+      <c r="B141" s="8" t="n">
         <v>43198</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D141" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E141" s="9" t="n">
+      <c r="D141" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" s="10" t="n">
         <v>1597</v>
       </c>
-      <c r="F141" s="9" t="n">
+      <c r="F141" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G141" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H141" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I141" s="9" t="n">
+      <c r="G141" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H141" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I141" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J141" s="9"/>
-      <c r="K141" s="9"/>
+      <c r="J141" s="10"/>
+      <c r="K141" s="10"/>
       <c r="L141" s="6"/>
       <c r="M141" s="6"/>
       <c r="N141" s="6"/>
@@ -5637,35 +5644,35 @@
       <c r="O142" s="6"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="7" t="n">
+      <c r="A143" s="8" t="n">
         <v>43209</v>
       </c>
-      <c r="B143" s="7" t="n">
+      <c r="B143" s="8" t="n">
         <v>43212</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D143" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E143" s="9" t="n">
+      <c r="D143" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E143" s="10" t="n">
         <v>2068</v>
       </c>
-      <c r="F143" s="9" t="n">
+      <c r="F143" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G143" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H143" s="9" t="n">
+      <c r="G143" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H143" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I143" s="9" t="n">
+      <c r="I143" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J143" s="9"/>
-      <c r="K143" s="9"/>
+      <c r="J143" s="10"/>
+      <c r="K143" s="10"/>
       <c r="L143" s="6"/>
       <c r="M143" s="6"/>
       <c r="N143" s="6"/>
@@ -5709,35 +5716,35 @@
       <c r="O144" s="6"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="7" t="n">
+      <c r="A145" s="8" t="n">
         <v>43221</v>
       </c>
-      <c r="B145" s="7" t="n">
+      <c r="B145" s="8" t="n">
         <v>43221</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D145" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E145" s="9" t="n">
+      <c r="D145" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E145" s="10" t="n">
         <v>2400</v>
       </c>
-      <c r="F145" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G145" s="9" t="n">
+      <c r="F145" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G145" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="H145" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I145" s="9" t="n">
+      <c r="H145" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I145" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J145" s="9"/>
-      <c r="K145" s="9"/>
+      <c r="J145" s="10"/>
+      <c r="K145" s="10"/>
       <c r="L145" s="6"/>
       <c r="M145" s="6"/>
       <c r="N145" s="6"/>
@@ -5781,35 +5788,35 @@
       <c r="O146" s="6"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="7" t="n">
+      <c r="A147" s="8" t="n">
         <v>43230</v>
       </c>
-      <c r="B147" s="7" t="n">
+      <c r="B147" s="8" t="n">
         <v>43233</v>
       </c>
-      <c r="C147" s="8" t="s">
+      <c r="C147" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D147" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E147" s="9" t="n">
+      <c r="D147" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E147" s="10" t="n">
         <v>1728</v>
       </c>
-      <c r="F147" s="9" t="n">
+      <c r="F147" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G147" s="9" t="n">
+      <c r="G147" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H147" s="9" t="n">
+      <c r="H147" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I147" s="9" t="n">
+      <c r="I147" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J147" s="9"/>
-      <c r="K147" s="9"/>
+      <c r="J147" s="10"/>
+      <c r="K147" s="10"/>
       <c r="L147" s="6"/>
       <c r="M147" s="6"/>
       <c r="N147" s="6"/>
@@ -5853,35 +5860,35 @@
       <c r="O148" s="6"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="7" t="n">
+      <c r="A149" s="8" t="n">
         <v>43230</v>
       </c>
-      <c r="B149" s="7" t="n">
+      <c r="B149" s="8" t="n">
         <v>43233</v>
       </c>
-      <c r="C149" s="8" t="s">
+      <c r="C149" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D149" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E149" s="9" t="n">
+      <c r="D149" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E149" s="10" t="n">
         <v>1200</v>
       </c>
-      <c r="F149" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G149" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H149" s="9" t="n">
+      <c r="F149" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G149" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H149" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I149" s="9" t="n">
+      <c r="I149" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J149" s="9"/>
-      <c r="K149" s="9"/>
+      <c r="J149" s="10"/>
+      <c r="K149" s="10"/>
       <c r="L149" s="6"/>
       <c r="M149" s="6"/>
       <c r="N149" s="6"/>
@@ -5925,35 +5932,35 @@
       <c r="O150" s="6"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="7" t="n">
+      <c r="A151" s="8" t="n">
         <v>43244</v>
       </c>
-      <c r="B151" s="7" t="n">
+      <c r="B151" s="8" t="n">
         <v>43247</v>
       </c>
-      <c r="C151" s="8" t="s">
+      <c r="C151" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D151" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E151" s="9" t="n">
+      <c r="D151" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E151" s="10" t="n">
         <v>1591</v>
       </c>
-      <c r="F151" s="9" t="n">
+      <c r="F151" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G151" s="9" t="n">
+      <c r="G151" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H151" s="9" t="n">
+      <c r="H151" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I151" s="9" t="n">
+      <c r="I151" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J151" s="9"/>
-      <c r="K151" s="9"/>
+      <c r="J151" s="10"/>
+      <c r="K151" s="10"/>
       <c r="L151" s="6"/>
       <c r="M151" s="6"/>
       <c r="N151" s="6"/>
@@ -5995,37 +6002,37 @@
       <c r="O152" s="6"/>
     </row>
     <row r="153" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="7" t="n">
+      <c r="A153" s="8" t="n">
         <v>43251</v>
       </c>
-      <c r="B153" s="7" t="n">
+      <c r="B153" s="8" t="n">
         <v>43254</v>
       </c>
-      <c r="C153" s="8" t="s">
+      <c r="C153" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D153" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E153" s="9" t="n">
+      <c r="D153" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E153" s="10" t="n">
         <v>1025</v>
       </c>
-      <c r="F153" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G153" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H153" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I153" s="9" t="n">
+      <c r="F153" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G153" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H153" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I153" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J153" s="9" t="n">
+      <c r="J153" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="K153" s="9"/>
+      <c r="K153" s="10"/>
       <c r="L153" s="6"/>
       <c r="M153" s="6"/>
       <c r="N153" s="6"/>
@@ -6069,35 +6076,35 @@
       <c r="O154" s="6"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="7" t="n">
+      <c r="A155" s="8" t="n">
         <v>43265</v>
       </c>
-      <c r="B155" s="7" t="n">
+      <c r="B155" s="8" t="n">
         <v>43268</v>
       </c>
-      <c r="C155" s="8" t="s">
+      <c r="C155" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D155" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E155" s="9" t="n">
+      <c r="D155" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E155" s="10" t="n">
         <v>1660</v>
       </c>
-      <c r="F155" s="9" t="n">
+      <c r="F155" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G155" s="9" t="n">
+      <c r="G155" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H155" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I155" s="9" t="n">
+      <c r="H155" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I155" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J155" s="9"/>
-      <c r="K155" s="9"/>
+      <c r="J155" s="10"/>
+      <c r="K155" s="10"/>
       <c r="L155" s="6"/>
       <c r="M155" s="6"/>
       <c r="N155" s="6"/>
@@ -6139,37 +6146,37 @@
       <c r="O156" s="6"/>
     </row>
     <row r="157" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="7" t="n">
+      <c r="A157" s="8" t="n">
         <v>43279</v>
       </c>
-      <c r="B157" s="7" t="n">
+      <c r="B157" s="8" t="n">
         <v>43282</v>
       </c>
-      <c r="C157" s="8" t="s">
+      <c r="C157" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D157" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E157" s="9" t="n">
+      <c r="D157" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E157" s="10" t="n">
         <v>1030</v>
       </c>
-      <c r="F157" s="9" t="n">
+      <c r="F157" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="G157" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H157" s="9" t="n">
+      <c r="G157" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H157" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I157" s="9" t="n">
+      <c r="I157" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J157" s="9" t="n">
+      <c r="J157" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K157" s="9"/>
+      <c r="K157" s="10"/>
       <c r="L157" s="6"/>
       <c r="M157" s="6"/>
       <c r="N157" s="6"/>
@@ -6213,35 +6220,35 @@
       <c r="O158" s="6"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="7" t="n">
+      <c r="A159" s="8" t="n">
         <v>43293</v>
       </c>
-      <c r="B159" s="7" t="n">
+      <c r="B159" s="8" t="n">
         <v>43296</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="C159" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D159" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E159" s="9" t="n">
+      <c r="D159" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E159" s="10" t="n">
         <v>1644</v>
       </c>
-      <c r="F159" s="9" t="n">
+      <c r="F159" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G159" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H159" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I159" s="9" t="n">
+      <c r="G159" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H159" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I159" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J159" s="9"/>
-      <c r="K159" s="9"/>
+      <c r="J159" s="10"/>
+      <c r="K159" s="10"/>
       <c r="L159" s="6"/>
       <c r="M159" s="6"/>
       <c r="N159" s="6"/>
@@ -6283,37 +6290,37 @@
       <c r="O160" s="6"/>
     </row>
     <row r="161" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="7" t="n">
+      <c r="A161" s="8" t="n">
         <v>43307</v>
       </c>
-      <c r="B161" s="7" t="n">
+      <c r="B161" s="8" t="n">
         <v>43310</v>
       </c>
-      <c r="C161" s="8" t="s">
+      <c r="C161" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D161" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E161" s="9" t="n">
+      <c r="D161" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E161" s="10" t="n">
         <v>1022</v>
       </c>
-      <c r="F161" s="9" t="n">
+      <c r="F161" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="G161" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H161" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I161" s="9" t="n">
+      <c r="G161" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H161" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I161" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J161" s="9" t="n">
+      <c r="J161" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K161" s="9"/>
+      <c r="K161" s="10"/>
       <c r="L161" s="6"/>
       <c r="M161" s="6"/>
       <c r="N161" s="6"/>
@@ -6355,35 +6362,35 @@
       <c r="O162" s="6"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="7" t="n">
+      <c r="A163" s="8" t="n">
         <v>43321</v>
       </c>
-      <c r="B163" s="7" t="n">
+      <c r="B163" s="8" t="n">
         <v>43324</v>
       </c>
-      <c r="C163" s="8" t="s">
+      <c r="C163" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D163" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E163" s="9" t="n">
+      <c r="D163" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E163" s="10" t="n">
         <v>1607</v>
       </c>
-      <c r="F163" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G163" s="9" t="n">
+      <c r="F163" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G163" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="H163" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I163" s="9" t="n">
+      <c r="H163" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I163" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J163" s="9"/>
-      <c r="K163" s="9"/>
+      <c r="J163" s="10"/>
+      <c r="K163" s="10"/>
       <c r="L163" s="6"/>
       <c r="M163" s="6"/>
       <c r="N163" s="6"/>
@@ -6427,35 +6434,35 @@
       <c r="O164" s="6"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="7" t="n">
+      <c r="A165" s="8" t="n">
         <v>43327</v>
       </c>
-      <c r="B165" s="7" t="n">
+      <c r="B165" s="8" t="n">
         <v>43330</v>
       </c>
-      <c r="C165" s="8" t="s">
+      <c r="C165" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D165" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E165" s="9" t="n">
+      <c r="D165" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E165" s="10" t="n">
         <v>1200</v>
       </c>
-      <c r="F165" s="9" t="n">
+      <c r="F165" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="G165" s="9" t="n">
+      <c r="G165" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="H165" s="9" t="n">
+      <c r="H165" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="I165" s="9" t="n">
+      <c r="I165" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J165" s="9"/>
-      <c r="K165" s="9"/>
+      <c r="J165" s="10"/>
+      <c r="K165" s="10"/>
       <c r="L165" s="6"/>
       <c r="M165" s="6"/>
       <c r="N165" s="6"/>
@@ -6499,35 +6506,35 @@
       <c r="O166" s="6"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="7" t="n">
+      <c r="A167" s="8" t="n">
         <v>43336</v>
       </c>
-      <c r="B167" s="7" t="n">
+      <c r="B167" s="8" t="n">
         <v>43338</v>
       </c>
-      <c r="C167" s="8" t="s">
+      <c r="C167" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D167" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E167" s="9" t="n">
+      <c r="D167" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E167" s="10" t="n">
         <v>1783</v>
       </c>
-      <c r="F167" s="9" t="n">
+      <c r="F167" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="G167" s="9" t="n">
+      <c r="G167" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="H167" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I167" s="9" t="n">
+      <c r="H167" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I167" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J167" s="9"/>
-      <c r="K167" s="9"/>
+      <c r="J167" s="10"/>
+      <c r="K167" s="10"/>
       <c r="L167" s="6"/>
       <c r="M167" s="6"/>
       <c r="N167" s="6"/>
@@ -6571,35 +6578,35 @@
       <c r="O168" s="6"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="7" t="n">
+      <c r="A169" s="8" t="n">
         <v>43349</v>
       </c>
-      <c r="B169" s="7" t="n">
+      <c r="B169" s="8" t="n">
         <v>43352</v>
       </c>
-      <c r="C169" s="8" t="s">
+      <c r="C169" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D169" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E169" s="9" t="n">
+      <c r="D169" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E169" s="10" t="n">
         <v>1653</v>
       </c>
-      <c r="F169" s="9" t="n">
+      <c r="F169" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="G169" s="9" t="n">
+      <c r="G169" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="H169" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I169" s="9" t="n">
+      <c r="H169" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I169" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J169" s="9"/>
-      <c r="K169" s="9"/>
+      <c r="J169" s="10"/>
+      <c r="K169" s="10"/>
       <c r="L169" s="6"/>
       <c r="M169" s="6"/>
       <c r="N169" s="6"/>
@@ -6641,37 +6648,37 @@
       <c r="O170" s="6"/>
     </row>
     <row r="171" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="7" t="n">
+      <c r="A171" s="8" t="n">
         <v>43363</v>
       </c>
-      <c r="B171" s="7" t="n">
+      <c r="B171" s="8" t="n">
         <v>43366</v>
       </c>
-      <c r="C171" s="8" t="s">
+      <c r="C171" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D171" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E171" s="9" t="n">
+      <c r="D171" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E171" s="10" t="n">
         <v>1030</v>
       </c>
-      <c r="F171" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G171" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H171" s="9" t="n">
+      <c r="F171" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G171" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H171" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="I171" s="9" t="n">
+      <c r="I171" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J171" s="9" t="n">
+      <c r="J171" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K171" s="9"/>
+      <c r="K171" s="10"/>
       <c r="L171" s="6"/>
       <c r="M171" s="6"/>
       <c r="N171" s="6"/>
@@ -6713,37 +6720,37 @@
       <c r="O172" s="6"/>
     </row>
     <row r="173" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="7" t="n">
+      <c r="A173" s="8" t="n">
         <v>43377</v>
       </c>
-      <c r="B173" s="7" t="n">
+      <c r="B173" s="8" t="n">
         <v>43380</v>
       </c>
-      <c r="C173" s="8" t="s">
+      <c r="C173" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D173" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E173" s="9" t="n">
+      <c r="D173" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E173" s="10" t="n">
         <v>1025</v>
       </c>
-      <c r="F173" s="9" t="n">
+      <c r="F173" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G173" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H173" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I173" s="9" t="n">
+      <c r="G173" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H173" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I173" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J173" s="9" t="n">
+      <c r="J173" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K173" s="9"/>
+      <c r="K173" s="10"/>
       <c r="L173" s="6"/>
       <c r="M173" s="6"/>
       <c r="N173" s="6"/>
@@ -6785,35 +6792,35 @@
       <c r="O174" s="6"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="7" t="n">
+      <c r="A175" s="8" t="n">
         <v>43384</v>
       </c>
-      <c r="B175" s="7" t="n">
+      <c r="B175" s="8" t="n">
         <v>43387</v>
       </c>
-      <c r="C175" s="8" t="s">
+      <c r="C175" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D175" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E175" s="9" t="n">
+      <c r="D175" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E175" s="10" t="n">
         <v>1707</v>
       </c>
-      <c r="F175" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G175" s="9" t="n">
+      <c r="F175" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G175" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H175" s="9" t="n">
+      <c r="H175" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I175" s="9" t="n">
+      <c r="I175" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J175" s="9"/>
-      <c r="K175" s="9"/>
+      <c r="J175" s="10"/>
+      <c r="K175" s="10"/>
       <c r="L175" s="6"/>
       <c r="M175" s="6"/>
       <c r="N175" s="6"/>
@@ -6855,35 +6862,35 @@
       <c r="O176" s="6"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="7" t="n">
+      <c r="A177" s="8" t="n">
         <v>43398</v>
       </c>
-      <c r="B177" s="7" t="n">
+      <c r="B177" s="8" t="n">
         <v>43401</v>
       </c>
-      <c r="C177" s="8" t="s">
+      <c r="C177" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D177" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E177" s="9" t="n">
+      <c r="D177" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E177" s="10" t="n">
         <v>1646</v>
       </c>
-      <c r="F177" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G177" s="9" t="n">
+      <c r="F177" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G177" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="H177" s="9" t="n">
+      <c r="H177" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I177" s="9" t="n">
+      <c r="I177" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J177" s="9"/>
-      <c r="K177" s="9"/>
+      <c r="J177" s="10"/>
+      <c r="K177" s="10"/>
       <c r="L177" s="6"/>
       <c r="M177" s="6"/>
       <c r="N177" s="6"/>
@@ -6925,35 +6932,35 @@
       <c r="O178" s="6"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="7" t="n">
+      <c r="A179" s="8" t="n">
         <v>43412</v>
       </c>
-      <c r="B179" s="7" t="n">
+      <c r="B179" s="8" t="n">
         <v>43415</v>
       </c>
-      <c r="C179" s="8" t="s">
+      <c r="C179" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D179" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E179" s="9" t="n">
+      <c r="D179" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E179" s="10" t="n">
         <v>1802</v>
       </c>
-      <c r="F179" s="9" t="n">
+      <c r="F179" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="G179" s="9" t="n">
+      <c r="G179" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="H179" s="9" t="n">
+      <c r="H179" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I179" s="9" t="n">
+      <c r="I179" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J179" s="9"/>
-      <c r="K179" s="9"/>
+      <c r="J179" s="10"/>
+      <c r="K179" s="10"/>
       <c r="L179" s="6"/>
       <c r="M179" s="6"/>
       <c r="N179" s="6"/>
@@ -6995,35 +7002,35 @@
       <c r="O180" s="6"/>
     </row>
     <row r="181" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="7" t="n">
+      <c r="A181" s="8" t="n">
         <v>43419</v>
       </c>
-      <c r="B181" s="7" t="n">
+      <c r="B181" s="8" t="n">
         <v>43422</v>
       </c>
-      <c r="C181" s="8" t="s">
+      <c r="C181" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D181" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E181" s="9" t="n">
+      <c r="D181" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E181" s="10" t="n">
         <v>1027</v>
       </c>
-      <c r="F181" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G181" s="9" t="n">
+      <c r="F181" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G181" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="H181" s="9" t="n">
+      <c r="H181" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I181" s="9" t="n">
+      <c r="I181" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J181" s="9"/>
-      <c r="K181" s="9"/>
+      <c r="J181" s="10"/>
+      <c r="K181" s="10"/>
       <c r="L181" s="6"/>
       <c r="M181" s="6"/>
       <c r="N181" s="6"/>
@@ -7065,35 +7072,35 @@
       <c r="O182" s="6"/>
     </row>
     <row r="183" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="7" t="n">
+      <c r="A183" s="8" t="n">
         <v>43432</v>
       </c>
-      <c r="B183" s="7" t="n">
+      <c r="B183" s="8" t="n">
         <v>43437</v>
       </c>
-      <c r="C183" s="8" t="s">
+      <c r="C183" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D183" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E183" s="9" t="n">
+      <c r="D183" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E183" s="10" t="n">
         <v>1032</v>
       </c>
-      <c r="F183" s="9" t="n">
+      <c r="F183" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G183" s="9" t="n">
+      <c r="G183" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="H183" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I183" s="9" t="n">
+      <c r="H183" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I183" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J183" s="9"/>
-      <c r="K183" s="9"/>
+      <c r="J183" s="10"/>
+      <c r="K183" s="10"/>
       <c r="L183" s="6"/>
       <c r="M183" s="6"/>
       <c r="N183" s="6"/>
@@ -7135,35 +7142,35 @@
       <c r="O184" s="6"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="7" t="n">
+      <c r="A185" s="8" t="n">
         <v>43446</v>
       </c>
-      <c r="B185" s="7" t="n">
+      <c r="B185" s="8" t="n">
         <v>43449</v>
       </c>
-      <c r="C185" s="8" t="s">
+      <c r="C185" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D185" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E185" s="9" t="n">
+      <c r="D185" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E185" s="10" t="n">
         <v>1200</v>
       </c>
-      <c r="F185" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G185" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H185" s="9" t="n">
+      <c r="F185" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G185" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H185" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="I185" s="9" t="n">
+      <c r="I185" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J185" s="9"/>
-      <c r="K185" s="9"/>
+      <c r="J185" s="10"/>
+      <c r="K185" s="10"/>
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
       <c r="N185" s="6"/>
@@ -7205,35 +7212,35 @@
       <c r="O186" s="6"/>
     </row>
     <row r="187" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="7" t="n">
+      <c r="A187" s="8" t="n">
         <v>43446</v>
       </c>
-      <c r="B187" s="7" t="n">
+      <c r="B187" s="8" t="n">
         <v>43451</v>
       </c>
-      <c r="C187" s="8" t="s">
+      <c r="C187" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D187" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E187" s="9" t="n">
+      <c r="D187" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E187" s="10" t="n">
         <v>1026</v>
       </c>
-      <c r="F187" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G187" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H187" s="9" t="n">
+      <c r="F187" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G187" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H187" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I187" s="9" t="n">
+      <c r="I187" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J187" s="9"/>
-      <c r="K187" s="9"/>
+      <c r="J187" s="10"/>
+      <c r="K187" s="10"/>
       <c r="L187" s="6"/>
       <c r="M187" s="6"/>
       <c r="N187" s="6"/>
@@ -7275,35 +7282,35 @@
       <c r="O188" s="6"/>
     </row>
     <row r="189" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="7" t="n">
+      <c r="A189" s="8" t="n">
         <v>43488</v>
       </c>
-      <c r="B189" s="7" t="n">
+      <c r="B189" s="8" t="n">
         <v>43496</v>
       </c>
-      <c r="C189" s="8" t="s">
+      <c r="C189" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D189" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E189" s="9" t="n">
+      <c r="D189" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E189" s="10" t="n">
         <v>1652</v>
       </c>
-      <c r="F189" s="9" t="n">
+      <c r="F189" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G189" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H189" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I189" s="9" t="n">
+      <c r="G189" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H189" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I189" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J189" s="9"/>
-      <c r="K189" s="9"/>
+      <c r="J189" s="10"/>
+      <c r="K189" s="10"/>
       <c r="L189" s="6"/>
       <c r="M189" s="6"/>
       <c r="N189" s="6"/>
@@ -7345,35 +7352,35 @@
       <c r="O190" s="6"/>
     </row>
     <row r="191" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="7" t="n">
+      <c r="A191" s="8" t="n">
         <v>43502</v>
       </c>
-      <c r="B191" s="7" t="n">
+      <c r="B191" s="8" t="n">
         <v>43507</v>
       </c>
-      <c r="C191" s="8" t="s">
+      <c r="C191" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D191" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E191" s="9" t="n">
+      <c r="D191" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E191" s="10" t="n">
         <v>1067</v>
       </c>
-      <c r="F191" s="9" t="n">
+      <c r="F191" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="G191" s="9" t="n">
+      <c r="G191" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="H191" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="I191" s="9" t="n">
+      <c r="H191" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I191" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J191" s="9"/>
-      <c r="K191" s="9"/>
+      <c r="J191" s="10"/>
+      <c r="K191" s="10"/>
       <c r="L191" s="6"/>
       <c r="M191" s="6"/>
       <c r="N191" s="6"/>
@@ -7415,35 +7422,35 @@
       <c r="O192" s="6"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="7" t="n">
+      <c r="A193" s="8" t="n">
         <v>43517</v>
       </c>
-      <c r="B193" s="7" t="n">
+      <c r="B193" s="8" t="n">
         <v>43520</v>
       </c>
-      <c r="C193" s="8" t="s">
+      <c r="C193" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D193" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E193" s="9" t="n">
+      <c r="D193" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E193" s="10" t="n">
         <v>1582</v>
       </c>
-      <c r="F193" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G193" s="9" t="n">
+      <c r="F193" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G193" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="H193" s="9" t="n">
+      <c r="H193" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I193" s="9" t="n">
+      <c r="I193" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J193" s="9"/>
-      <c r="K193" s="9"/>
+      <c r="J193" s="10"/>
+      <c r="K193" s="10"/>
       <c r="L193" s="6"/>
       <c r="M193" s="6"/>
       <c r="N193" s="6"/>
@@ -7485,35 +7492,35 @@
       <c r="O194" s="6"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="7" t="n">
+      <c r="A195" s="8" t="n">
         <v>43531</v>
       </c>
-      <c r="B195" s="7" t="n">
+      <c r="B195" s="8" t="n">
         <v>43534</v>
       </c>
-      <c r="C195" s="8" t="s">
+      <c r="C195" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D195" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E195" s="9" t="n">
+      <c r="D195" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E195" s="10" t="n">
         <v>1610</v>
       </c>
-      <c r="F195" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G195" s="9" t="n">
+      <c r="F195" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G195" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="H195" s="9" t="n">
+      <c r="H195" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I195" s="9" t="n">
+      <c r="I195" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J195" s="9"/>
-      <c r="K195" s="9"/>
+      <c r="J195" s="10"/>
+      <c r="K195" s="10"/>
       <c r="L195" s="6"/>
       <c r="M195" s="6"/>
       <c r="N195" s="6"/>
@@ -7559,35 +7566,35 @@
       <c r="O196" s="6"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="7" t="n">
+      <c r="A197" s="8" t="n">
         <v>43559</v>
       </c>
-      <c r="B197" s="7" t="n">
+      <c r="B197" s="8" t="n">
         <v>43562</v>
       </c>
-      <c r="C197" s="8" t="s">
+      <c r="C197" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D197" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E197" s="9" t="n">
+      <c r="D197" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E197" s="10" t="n">
         <v>1799</v>
       </c>
-      <c r="F197" s="9" t="n">
+      <c r="F197" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G197" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H197" s="9" t="n">
+      <c r="G197" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H197" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I197" s="9" t="n">
+      <c r="I197" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J197" s="9"/>
-      <c r="K197" s="9" t="n">
+      <c r="J197" s="10"/>
+      <c r="K197" s="10" t="n">
         <v>2</v>
       </c>
       <c r="L197" s="6"/>
@@ -7631,35 +7638,35 @@
       <c r="O198" s="6"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="7" t="n">
+      <c r="A199" s="8" t="n">
         <v>43559</v>
       </c>
-      <c r="B199" s="7" t="n">
+      <c r="B199" s="8" t="n">
         <v>43562</v>
       </c>
-      <c r="C199" s="8" t="s">
+      <c r="C199" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D199" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E199" s="9" t="n">
+      <c r="D199" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E199" s="10" t="n">
         <v>1200</v>
       </c>
-      <c r="F199" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G199" s="9" t="n">
+      <c r="F199" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G199" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="H199" s="9" t="n">
+      <c r="H199" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="I199" s="9" t="n">
+      <c r="I199" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J199" s="9"/>
-      <c r="K199" s="9"/>
+      <c r="J199" s="10"/>
+      <c r="K199" s="10"/>
       <c r="L199" s="6"/>
       <c r="M199" s="6"/>
       <c r="N199" s="6"/>
@@ -7703,35 +7710,35 @@
       <c r="O200" s="6"/>
     </row>
     <row r="201" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="7" t="n">
+      <c r="A201" s="8" t="n">
         <v>43578</v>
       </c>
-      <c r="B201" s="7" t="n">
+      <c r="B201" s="8" t="n">
         <v>43580</v>
       </c>
-      <c r="C201" s="8" t="s">
+      <c r="C201" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D201" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E201" s="9" t="n">
+      <c r="D201" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E201" s="10" t="n">
         <v>1012</v>
       </c>
-      <c r="F201" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G201" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H201" s="9" t="n">
+      <c r="F201" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G201" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H201" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I201" s="9" t="n">
+      <c r="I201" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="J201" s="9"/>
-      <c r="K201" s="9" t="n">
+      <c r="J201" s="10"/>
+      <c r="K201" s="10" t="n">
         <v>4</v>
       </c>
       <c r="L201" s="6"/>
@@ -7777,35 +7784,35 @@
       <c r="O202" s="6"/>
     </row>
     <row r="203" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="7" t="n">
+      <c r="A203" s="8" t="n">
         <v>43579</v>
       </c>
-      <c r="B203" s="7" t="n">
+      <c r="B203" s="8" t="n">
         <v>43584</v>
       </c>
-      <c r="C203" s="8" t="s">
+      <c r="C203" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D203" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E203" s="9" t="n">
+      <c r="D203" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E203" s="10" t="n">
         <v>1010</v>
       </c>
-      <c r="F203" s="9" t="n">
+      <c r="F203" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G203" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H203" s="9" t="n">
+      <c r="G203" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H203" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I203" s="9" t="n">
+      <c r="I203" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J203" s="9"/>
-      <c r="K203" s="9"/>
+      <c r="J203" s="10"/>
+      <c r="K203" s="10"/>
       <c r="L203" s="6"/>
       <c r="M203" s="6"/>
       <c r="N203" s="6"/>
@@ -7847,35 +7854,35 @@
       <c r="O204" s="6"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="7" t="n">
+      <c r="A205" s="8" t="n">
         <v>43587</v>
       </c>
-      <c r="B205" s="7" t="n">
+      <c r="B205" s="8" t="n">
         <v>43590</v>
       </c>
-      <c r="C205" s="8" t="s">
+      <c r="C205" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D205" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E205" s="9" t="n">
+      <c r="D205" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E205" s="10" t="n">
         <v>2003</v>
       </c>
-      <c r="F205" s="9" t="n">
+      <c r="F205" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="G205" s="9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H205" s="9" t="n">
+      <c r="G205" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H205" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I205" s="9" t="n">
+      <c r="I205" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J205" s="9"/>
-      <c r="K205" s="9" t="n">
+      <c r="J205" s="10"/>
+      <c r="K205" s="10" t="n">
         <v>4</v>
       </c>
       <c r="L205" s="6"/>
@@ -7919,35 +7926,35 @@
       <c r="O206" s="6"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="7" t="n">
+      <c r="A207" s="8" t="n">
         <v>43594</v>
       </c>
-      <c r="B207" s="7" t="n">
+      <c r="B207" s="8" t="n">
         <v>43596</v>
       </c>
-      <c r="C207" s="8" t="s">
+      <c r="C207" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D207" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E207" s="9" t="n">
+      <c r="D207" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E207" s="10" t="n">
         <v>1644</v>
       </c>
-      <c r="F207" s="9" t="n">
+      <c r="F207" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G207" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="H207" s="9" t="n">
+      <c r="G207" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H207" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I207" s="9" t="n">
+      <c r="I207" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="J207" s="9"/>
-      <c r="K207" s="9" t="n">
+      <c r="J207" s="10"/>
+      <c r="K207" s="10" t="n">
         <v>4</v>
       </c>
       <c r="L207" s="6"/>
@@ -7991,35 +7998,35 @@
       <c r="O208" s="6"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="7" t="n">
+      <c r="A209" s="8" t="n">
         <v>43597</v>
       </c>
-      <c r="B209" s="7" t="n">
+      <c r="B209" s="8" t="n">
         <v>43600</v>
       </c>
-      <c r="C209" s="8" t="s">
+      <c r="C209" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D209" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E209" s="9" t="n">
+      <c r="D209" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E209" s="10" t="n">
         <v>1842</v>
       </c>
-      <c r="F209" s="9" t="n">
+      <c r="F209" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="G209" s="9" t="n">
+      <c r="G209" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="H209" s="9" t="n">
+      <c r="H209" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="I209" s="9" t="n">
+      <c r="I209" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="J209" s="9"/>
-      <c r="K209" s="9"/>
+      <c r="J209" s="10"/>
+      <c r="K209" s="10"/>
       <c r="L209" s="6"/>
       <c r="M209" s="6"/>
       <c r="N209" s="6"/>
@@ -8063,294 +8070,294 @@
       <c r="O210" s="6"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="10" t="n">
+      <c r="A211" s="11" t="n">
         <v>43599</v>
       </c>
-      <c r="B211" s="10" t="n">
+      <c r="B211" s="11" t="n">
         <v>43602</v>
       </c>
-      <c r="C211" s="11" t="s">
+      <c r="C211" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D211" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E211" s="12" t="n">
+      <c r="D211" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E211" s="13" t="n">
         <v>3038</v>
       </c>
-      <c r="F211" s="12" t="n">
+      <c r="F211" s="13" t="n">
         <v>38</v>
       </c>
-      <c r="G211" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="H211" s="12" t="n">
+      <c r="G211" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="H211" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="I211" s="12" t="n">
+      <c r="I211" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="J211" s="12"/>
-      <c r="K211" s="12" t="n">
+      <c r="J211" s="13"/>
+      <c r="K211" s="13" t="n">
         <v>5</v>
       </c>
       <c r="L211" s="6"/>
       <c r="M211" s="6"/>
-      <c r="N211" s="13"/>
-      <c r="O211" s="13"/>
+      <c r="N211" s="14"/>
+      <c r="O211" s="14"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="14" t="n">
+      <c r="A212" s="15" t="n">
         <v>43595</v>
       </c>
-      <c r="B212" s="14" t="n">
+      <c r="B212" s="15" t="n">
         <v>43597</v>
       </c>
-      <c r="C212" s="15" t="s">
+      <c r="C212" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D212" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F212" s="0" t="n">
+      <c r="D212" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F212" s="14" t="n">
         <v>38.5</v>
       </c>
-      <c r="G212" s="0" t="n">
+      <c r="G212" s="14" t="n">
         <v>35.5</v>
       </c>
-      <c r="H212" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="I212" s="0" t="n">
+      <c r="H212" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I212" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="K212" s="0" t="n">
+      <c r="K212" s="14" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="14" t="n">
+      <c r="A213" s="15" t="n">
         <v>43589</v>
       </c>
-      <c r="B213" s="14" t="n">
+      <c r="B213" s="15" t="n">
         <v>43590</v>
       </c>
-      <c r="C213" s="15" t="s">
+      <c r="C213" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F213" s="0" t="n">
+      <c r="F213" s="14" t="n">
         <v>38.5</v>
       </c>
-      <c r="G213" s="0" t="n">
+      <c r="G213" s="14" t="n">
         <v>34</v>
       </c>
-      <c r="H213" s="0" t="n">
+      <c r="H213" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="I213" s="0" t="n">
+      <c r="I213" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="K213" s="0" t="n">
+      <c r="K213" s="14" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="14" t="n">
+      <c r="A214" s="15" t="n">
         <v>43582</v>
       </c>
-      <c r="B214" s="14" t="n">
+      <c r="B214" s="15" t="n">
         <v>43583</v>
       </c>
-      <c r="C214" s="15" t="s">
+      <c r="C214" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D214" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F214" s="0" t="n">
+      <c r="D214" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F214" s="14" t="n">
         <v>39.5</v>
       </c>
-      <c r="G214" s="0" t="n">
-        <v>36</v>
-      </c>
-      <c r="H214" s="0" t="n">
+      <c r="G214" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="H214" s="14" t="n">
         <v>9.5</v>
       </c>
-      <c r="I214" s="0" t="n">
+      <c r="I214" s="14" t="n">
         <v>2.5</v>
       </c>
-      <c r="K214" s="0" t="n">
+      <c r="K214" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="14" t="n">
+      <c r="A215" s="15" t="n">
         <v>43575</v>
       </c>
-      <c r="B215" s="14" t="n">
+      <c r="B215" s="15" t="n">
         <v>43576</v>
       </c>
-      <c r="C215" s="15" t="s">
+      <c r="C215" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F215" s="0" t="n">
+      <c r="F215" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="G215" s="0" t="n">
+      <c r="G215" s="14" t="n">
         <v>35.5</v>
       </c>
-      <c r="H215" s="0" t="n">
+      <c r="H215" s="14" t="n">
         <v>9.5</v>
       </c>
-      <c r="I215" s="0" t="n">
+      <c r="I215" s="14" t="n">
         <v>4.5</v>
       </c>
-      <c r="K215" s="0" t="n">
+      <c r="K215" s="14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="14" t="n">
+      <c r="A216" s="15" t="n">
         <v>43561</v>
       </c>
-      <c r="B216" s="14" t="n">
+      <c r="B216" s="15" t="n">
         <v>43562</v>
       </c>
-      <c r="C216" s="15" t="s">
+      <c r="C216" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D216" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F216" s="0" t="n">
-        <v>37</v>
-      </c>
-      <c r="G216" s="0" t="n">
+      <c r="D216" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F216" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="G216" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="H216" s="0" t="n">
+      <c r="H216" s="14" t="n">
         <v>13.5</v>
       </c>
-      <c r="I216" s="0" t="n">
+      <c r="I216" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="K216" s="0" t="n">
+      <c r="K216" s="14" t="n">
         <v>1.5</v>
       </c>
-      <c r="L216" s="0" t="n">
+      <c r="L216" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="M216" s="0" t="n">
+      <c r="M216" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="14" t="n">
+      <c r="A217" s="15" t="n">
         <v>43337</v>
       </c>
-      <c r="B217" s="14" t="n">
+      <c r="B217" s="15" t="n">
         <v>43703</v>
       </c>
-      <c r="C217" s="15" t="s">
+      <c r="C217" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F217" s="0" t="n">
+      <c r="F217" s="14" t="n">
         <v>36.5</v>
       </c>
-      <c r="G217" s="0" t="n">
-        <v>36</v>
-      </c>
-      <c r="H217" s="0" t="n">
+      <c r="G217" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="H217" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="I217" s="0" t="n">
+      <c r="I217" s="14" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="14" t="n">
+      <c r="A218" s="15" t="n">
         <v>43183</v>
       </c>
-      <c r="B218" s="14" t="n">
+      <c r="B218" s="15" t="n">
         <v>43191</v>
       </c>
-      <c r="C218" s="15" t="s">
+      <c r="C218" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D218" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F218" s="0" t="n">
+      <c r="D218" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F218" s="14" t="n">
         <v>38.5</v>
       </c>
-      <c r="G218" s="0" t="n">
+      <c r="G218" s="14" t="n">
         <v>37.5</v>
       </c>
-      <c r="H218" s="0" t="n">
+      <c r="H218" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="I218" s="0" t="n">
+      <c r="I218" s="14" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="14" t="n">
+      <c r="A219" s="15" t="n">
         <v>43176</v>
       </c>
-      <c r="B219" s="14" t="n">
+      <c r="B219" s="15" t="n">
         <v>43184</v>
       </c>
-      <c r="C219" s="15" t="s">
+      <c r="C219" s="16" t="s">
         <v>21</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F219" s="0" t="n">
+      <c r="F219" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="G219" s="0" t="n">
+      <c r="G219" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="H219" s="0" t="n">
+      <c r="H219" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="I219" s="0" t="n">
+      <c r="I219" s="14" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="14" t="n">
+      <c r="A220" s="15" t="n">
         <v>43162</v>
       </c>
-      <c r="B220" s="14" t="n">
+      <c r="B220" s="15" t="n">
         <v>43170</v>
       </c>
-      <c r="C220" s="15" t="s">
+      <c r="C220" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D220" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F220" s="0" t="n">
-        <v>36</v>
-      </c>
-      <c r="G220" s="0" t="n">
-        <v>36</v>
-      </c>
-      <c r="H220" s="0" t="n">
+      <c r="D220" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F220" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G220" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="H220" s="14" t="n">
         <v>13.5</v>
       </c>
-      <c r="I220" s="0" t="n">
+      <c r="I220" s="14" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8358,10 +8365,10 @@
       <c r="D221" s="4"/>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D222" s="8"/>
+      <c r="D222" s="9"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D223" s="8"/>
+      <c r="D223" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
